--- a/REPORTING MODULE/product file.xlsx
+++ b/REPORTING MODULE/product file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\J S DASH\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY WORK FLOW\Emyris Onboard App\REPORTING MODULE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01F1302-8972-4392-8644-D834751E3C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E8C54D-36B6-40A1-8D03-BD489FF23440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>Sr no.</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>UID</t>
-  </si>
-  <si>
     <t>Stock</t>
   </si>
   <si>
@@ -54,423 +51,240 @@
     <t>PTR</t>
   </si>
   <si>
-    <t>View</t>
-  </si>
-  <si>
-    <t>Actions</t>
-  </si>
-  <si>
     <t>Alomos Hp 30gm Sachet</t>
   </si>
   <si>
-    <t>PDT23</t>
-  </si>
-  <si>
-    <t>Critiza</t>
-  </si>
-  <si>
     <t>30 Gm</t>
   </si>
   <si>
     <t>Emycef Fort 3gm</t>
   </si>
   <si>
-    <t>PDT32</t>
-  </si>
-  <si>
     <t>1 Vail</t>
   </si>
   <si>
     <t>Alomos Oral Albumin Powder(v)</t>
   </si>
   <si>
-    <t>PDT24</t>
-  </si>
-  <si>
     <t>400 Gm</t>
   </si>
   <si>
     <t>Edopen 1.125 Inj</t>
   </si>
   <si>
-    <t>PDT25</t>
-  </si>
-  <si>
     <t>Alomos St Powder(400 Gm)</t>
   </si>
   <si>
-    <t>PDT26</t>
-  </si>
-  <si>
     <t>Ciltum 3gm Inj</t>
   </si>
   <si>
-    <t>PDT27</t>
-  </si>
-  <si>
     <t>3gm Inj</t>
   </si>
   <si>
     <t>Alomos Dm Powder(400 Gm)</t>
   </si>
   <si>
-    <t>PDT22</t>
-  </si>
-  <si>
     <t>Ascocid 1.5gm Inj</t>
   </si>
   <si>
-    <t>PDT30</t>
-  </si>
-  <si>
     <t>1.5gm</t>
   </si>
   <si>
     <t>Alomos Oral Albumin (15gm)</t>
   </si>
   <si>
-    <t>PDT29</t>
-  </si>
-  <si>
     <t>15 Gm</t>
   </si>
   <si>
     <t>Alomos Hp Powder</t>
   </si>
   <si>
-    <t>PDT28</t>
-  </si>
-  <si>
     <t>Emynem 1gm</t>
   </si>
   <si>
-    <t>PDT33</t>
-  </si>
-  <si>
     <t>Ciltum 1.5gm Inj</t>
   </si>
   <si>
-    <t>PDT31</t>
-  </si>
-  <si>
     <t>1.5gm Inj</t>
   </si>
   <si>
     <t>Emynem 500mg</t>
   </si>
   <si>
-    <t>PDT34</t>
-  </si>
-  <si>
     <t>Emynem Sb 1.5gm Inj</t>
   </si>
   <si>
-    <t>PDT36</t>
-  </si>
-  <si>
     <t>Emynem Plus 1gm Inj</t>
   </si>
   <si>
-    <t>PDT35</t>
-  </si>
-  <si>
     <t>Emypip 4.5gm</t>
   </si>
   <si>
-    <t>PDT37</t>
-  </si>
-  <si>
     <t>Emystin 3 Miu</t>
   </si>
   <si>
-    <t>PDT38</t>
-  </si>
-  <si>
     <t>Murafos 4gm</t>
   </si>
   <si>
-    <t>PDT39</t>
-  </si>
-  <si>
     <t>Tigazz 100mg Inj</t>
   </si>
   <si>
-    <t>PDT43</t>
-  </si>
-  <si>
     <t>Pakris 7.5lac</t>
   </si>
   <si>
-    <t>PDT41</t>
-  </si>
-  <si>
     <t>Pakris 5lac</t>
   </si>
   <si>
-    <t>PDT40</t>
-  </si>
-  <si>
     <t>Ribloc 100mg Inj</t>
   </si>
   <si>
-    <t>PDT42</t>
-  </si>
-  <si>
     <t>Tigazz 50mg</t>
   </si>
   <si>
-    <t>PDT44</t>
-  </si>
-  <si>
     <t>Emycef 3gm</t>
   </si>
   <si>
-    <t>PDT45</t>
-  </si>
-  <si>
     <t>Emycef 1.5gm</t>
   </si>
   <si>
-    <t>PDT46</t>
-  </si>
-  <si>
     <t>Alomos Mama(choco) 200gm</t>
   </si>
   <si>
-    <t>PDT2</t>
-  </si>
-  <si>
     <t>200gm</t>
   </si>
   <si>
     <t>Alomos St Pouch(samples)</t>
   </si>
   <si>
-    <t>PDT47</t>
-  </si>
-  <si>
     <t>30gm</t>
   </si>
   <si>
     <t>Alomos Hp Sachet(samples)</t>
   </si>
   <si>
-    <t>PDT48</t>
-  </si>
-  <si>
     <t>Alomos Dm Sachet(sample)</t>
   </si>
   <si>
-    <t>PDT49</t>
-  </si>
-  <si>
     <t>Alomos Oral Albumin Sachet(sample)</t>
   </si>
   <si>
-    <t>PDT50</t>
-  </si>
-  <si>
     <t>15gm</t>
   </si>
   <si>
     <t>Alomos Mama Sachet(sample)</t>
   </si>
   <si>
-    <t>PDT51</t>
-  </si>
-  <si>
     <t>Emyrin Syp(150ml)</t>
   </si>
   <si>
-    <t>PDT3</t>
-  </si>
-  <si>
     <t>150 Ml</t>
   </si>
   <si>
     <t>Emycef Fort 1.5gm</t>
   </si>
   <si>
-    <t>PDT4</t>
-  </si>
-  <si>
     <t>Vial</t>
   </si>
   <si>
     <t>Alomos Nc Powder(400gm)</t>
   </si>
   <si>
-    <t>PDT5</t>
-  </si>
-  <si>
     <t>Alomos Mama(icecream) 200gm</t>
   </si>
   <si>
-    <t>PDT52</t>
-  </si>
-  <si>
     <t>Ncityl Tab 600mg (1x10) Strips</t>
   </si>
   <si>
-    <t>PDT6</t>
-  </si>
-  <si>
     <t>1x10 Tab Strips</t>
   </si>
   <si>
     <t>Emytaz 2.5gm</t>
   </si>
   <si>
-    <t>PDT53</t>
-  </si>
-  <si>
     <t>1 Vial</t>
   </si>
   <si>
     <t>Neupop-o</t>
   </si>
   <si>
-    <t>PDT54</t>
-  </si>
-  <si>
     <t>200ml</t>
   </si>
   <si>
     <t>Ncityl 2ml Amp</t>
   </si>
   <si>
-    <t>PDT7</t>
-  </si>
-  <si>
     <t>(1bxx5amp)</t>
   </si>
   <si>
     <t>Ncityl 5ml Amp</t>
   </si>
   <si>
-    <t>PDT8</t>
-  </si>
-  <si>
     <t>Blinza 1gm</t>
   </si>
   <si>
-    <t>PDT55</t>
-  </si>
-  <si>
     <t>Gulpcdz(1x30tab)</t>
   </si>
   <si>
-    <t>PDT9</t>
-  </si>
-  <si>
     <t>1x30 Tab Btl450</t>
   </si>
   <si>
     <t>Cylvex 100mg</t>
   </si>
   <si>
-    <t>PDT56</t>
-  </si>
-  <si>
     <t>Planicid 400mg</t>
   </si>
   <si>
-    <t>PDT57</t>
-  </si>
-  <si>
     <t>Glutenza 600mg</t>
   </si>
   <si>
-    <t>PDT58</t>
-  </si>
-  <si>
     <t>Curizaa 100mg</t>
   </si>
   <si>
-    <t>PDT10</t>
-  </si>
-  <si>
     <t>Aavizza 2.5gm</t>
   </si>
   <si>
-    <t>PDT11</t>
-  </si>
-  <si>
     <t>Alomos Oral Albumen 400gm(m)</t>
   </si>
   <si>
-    <t>PDT12</t>
-  </si>
-  <si>
     <t>400gm</t>
   </si>
   <si>
     <t>Eazex-m</t>
   </si>
   <si>
-    <t>PDT59</t>
-  </si>
-  <si>
     <t>Glowvit-60k Nano Shot</t>
   </si>
   <si>
-    <t>PDT60</t>
-  </si>
-  <si>
     <t>(1x4x5ml)</t>
   </si>
   <si>
     <t>Emytaz 1.5gm</t>
   </si>
   <si>
-    <t>PDT61</t>
-  </si>
-  <si>
     <t>Alomos Hp Advanced</t>
   </si>
   <si>
-    <t>PDT62</t>
-  </si>
-  <si>
     <t>Alomos Mama (k&amp;e)</t>
   </si>
   <si>
-    <t>PDT63</t>
-  </si>
-  <si>
     <t>Planicid 600mg</t>
   </si>
   <si>
-    <t>PDT64</t>
-  </si>
-  <si>
     <t>Emynem Tz</t>
   </si>
   <si>
-    <t>PDT65</t>
-  </si>
-  <si>
     <t>Tigixin 100mg</t>
   </si>
   <si>
-    <t>PDT13</t>
-  </si>
-  <si>
     <t>Alomos Gold</t>
   </si>
   <si>
-    <t>PDT14</t>
-  </si>
-  <si>
     <t>1 Kg</t>
   </si>
   <si>
     <t>Murafos 8gm (sachet)</t>
   </si>
   <si>
-    <t>PDT15</t>
-  </si>
-  <si>
     <t>8gm Sachet</t>
   </si>
   <si>
@@ -484,6 +298,9 @@
   </si>
   <si>
     <t>Approved By</t>
+  </si>
+  <si>
+    <t>CRITIZA</t>
   </si>
 </sst>
 </file>
@@ -860,13 +677,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -891,788 +708,701 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>90</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>54.92</v>
       </c>
       <c r="H2">
-        <v>54.92</v>
-      </c>
-      <c r="I2">
         <v>61.02</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>1499</v>
       </c>
       <c r="G3">
-        <v>1499</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>90</v>
-      </c>
-      <c r="I3">
         <v>1070.71</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
+      <c r="F4">
+        <v>1751</v>
       </c>
       <c r="G4">
-        <v>1751</v>
+        <v>1068.4100000000001</v>
       </c>
       <c r="H4">
-        <v>1068.4100000000001</v>
-      </c>
-      <c r="I4">
         <v>1187.1199999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>1599</v>
       </c>
       <c r="G5">
-        <v>1599</v>
+        <v>450</v>
       </c>
       <c r="H5">
-        <v>450</v>
-      </c>
-      <c r="I5">
         <v>1142.1400000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
+      <c r="F6">
+        <v>999</v>
       </c>
       <c r="G6">
-        <v>999</v>
+        <v>609.55999999999995</v>
       </c>
       <c r="H6">
-        <v>609.55999999999995</v>
-      </c>
-      <c r="I6">
         <v>677.29</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>790</v>
       </c>
       <c r="G7">
-        <v>790</v>
+        <v>150</v>
       </c>
       <c r="H7">
-        <v>150</v>
-      </c>
-      <c r="I7">
         <v>564.29</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
+      <c r="F8">
+        <v>899</v>
       </c>
       <c r="G8">
-        <v>899</v>
+        <v>548.54</v>
       </c>
       <c r="H8">
-        <v>548.54</v>
-      </c>
-      <c r="I8">
         <v>609.49</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>330</v>
       </c>
       <c r="G9">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="H9">
-        <v>65</v>
-      </c>
-      <c r="I9">
         <v>235.71</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>85</v>
       </c>
       <c r="G10">
-        <v>85</v>
+        <v>51.86</v>
       </c>
       <c r="H10">
-        <v>51.86</v>
-      </c>
-      <c r="I10">
         <v>57.63</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
+      <c r="F11">
+        <v>1249</v>
       </c>
       <c r="G11">
-        <v>1249</v>
+        <v>762.1</v>
       </c>
       <c r="H11">
-        <v>762.1</v>
-      </c>
-      <c r="I11">
         <v>846.76</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>551</v>
       </c>
       <c r="G12">
-        <v>551</v>
+        <v>160</v>
       </c>
       <c r="H12">
-        <v>160</v>
-      </c>
-      <c r="I12">
         <v>393.57</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+      <c r="F13">
+        <v>491</v>
       </c>
       <c r="G13">
-        <v>491</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
-      </c>
-      <c r="I13">
         <v>350.71</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <v>471</v>
       </c>
       <c r="G14">
-        <v>471</v>
+        <v>126</v>
       </c>
       <c r="H14">
-        <v>126</v>
-      </c>
-      <c r="I14">
         <v>336.43</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>2499</v>
       </c>
       <c r="G15">
-        <v>2499</v>
+        <v>450</v>
       </c>
       <c r="H15">
-        <v>450</v>
-      </c>
-      <c r="I15">
         <v>1785</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F16">
+        <v>1067</v>
       </c>
       <c r="G16">
-        <v>1067</v>
+        <v>160</v>
       </c>
       <c r="H16">
-        <v>160</v>
-      </c>
-      <c r="I16">
         <v>762.14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F17">
+        <v>447.31</v>
       </c>
       <c r="G17">
-        <v>447.31</v>
+        <v>76</v>
       </c>
       <c r="H17">
-        <v>76</v>
-      </c>
-      <c r="I17">
         <v>336.65</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>6800</v>
       </c>
       <c r="G18">
-        <v>6800</v>
+        <v>500</v>
       </c>
       <c r="H18">
-        <v>500</v>
-      </c>
-      <c r="I18">
         <v>4857.1400000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F19">
+        <v>1999</v>
       </c>
       <c r="G19">
-        <v>1999</v>
+        <v>800</v>
       </c>
       <c r="H19">
-        <v>800</v>
-      </c>
-      <c r="I19">
         <v>1427.86</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F20">
+        <v>2990</v>
       </c>
       <c r="G20">
-        <v>2990</v>
+        <v>900</v>
       </c>
       <c r="H20">
-        <v>900</v>
-      </c>
-      <c r="I20">
         <v>2135.71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F21">
+        <v>3938</v>
       </c>
       <c r="G21">
-        <v>3938</v>
+        <v>630</v>
       </c>
       <c r="H21">
-        <v>630</v>
-      </c>
-      <c r="I21">
         <v>2812.86</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F22">
+        <v>2431</v>
       </c>
       <c r="G22">
-        <v>2431</v>
+        <v>315</v>
       </c>
       <c r="H22">
-        <v>315</v>
-      </c>
-      <c r="I22">
         <v>1736.43</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>3576</v>
       </c>
       <c r="G23">
-        <v>3576</v>
+        <v>630</v>
       </c>
       <c r="H23">
-        <v>630</v>
-      </c>
-      <c r="I23">
         <v>2554.29</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>1499</v>
       </c>
       <c r="G24">
-        <v>1499</v>
+        <v>315</v>
       </c>
       <c r="H24">
-        <v>315</v>
-      </c>
-      <c r="I24">
         <v>1070.71</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F25">
+        <v>859</v>
       </c>
       <c r="G25">
-        <v>859</v>
+        <v>90</v>
       </c>
       <c r="H25">
-        <v>90</v>
-      </c>
-      <c r="I25">
         <v>613.57000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>331</v>
       </c>
       <c r="G26">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="H26">
-        <v>38</v>
-      </c>
-      <c r="I26">
         <v>236.43</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="F27">
+        <v>429</v>
       </c>
       <c r="G27">
-        <v>429</v>
+        <v>261.76</v>
       </c>
       <c r="H27">
-        <v>261.76</v>
-      </c>
-      <c r="I27">
         <v>290.85000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1680,28 +1410,25 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1709,28 +1436,25 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1738,28 +1462,25 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" t="s">
-        <v>81</v>
+        <v>47</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1767,28 +1488,25 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" t="s">
-        <v>74</v>
+        <v>43</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1796,818 +1514,733 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
-        <v>86</v>
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>2849</v>
       </c>
       <c r="G33">
-        <v>2849</v>
+        <v>1200</v>
       </c>
       <c r="H33">
-        <v>1200</v>
-      </c>
-      <c r="I33">
         <v>1931.53</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s">
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
+        <v>52</v>
+      </c>
+      <c r="F34">
+        <v>990</v>
       </c>
       <c r="G34">
-        <v>990</v>
+        <v>170</v>
       </c>
       <c r="H34">
-        <v>170</v>
-      </c>
-      <c r="I34">
         <v>636.42999999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>91</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
       </c>
-      <c r="F35" t="s">
-        <v>20</v>
+      <c r="F35">
+        <v>1149</v>
       </c>
       <c r="G35">
-        <v>1149</v>
+        <v>701.08</v>
       </c>
       <c r="H35">
-        <v>701.08</v>
-      </c>
-      <c r="I35">
         <v>778.98</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="F36">
+        <v>429</v>
       </c>
       <c r="G36">
-        <v>429</v>
+        <v>261.76</v>
       </c>
       <c r="H36">
-        <v>261.76</v>
-      </c>
-      <c r="I36">
         <v>290.85000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>91</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
+        <v>56</v>
+      </c>
+      <c r="F37">
+        <v>249.2</v>
       </c>
       <c r="G37">
-        <v>249.2</v>
+        <v>152.05000000000001</v>
       </c>
       <c r="H37">
-        <v>152.05000000000001</v>
-      </c>
-      <c r="I37">
         <v>168.95</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38" t="s">
+        <v>91</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F38">
+        <v>1499</v>
       </c>
       <c r="G38">
-        <v>1499</v>
+        <v>963.64</v>
       </c>
       <c r="H38">
-        <v>963.64</v>
-      </c>
-      <c r="I38">
         <v>1070.71</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39" t="s">
+        <v>91</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" t="s">
-        <v>102</v>
+        <v>60</v>
+      </c>
+      <c r="F39">
+        <v>1049</v>
       </c>
       <c r="G39">
-        <v>1049</v>
+        <v>640.07000000000005</v>
       </c>
       <c r="H39">
-        <v>640.07000000000005</v>
-      </c>
-      <c r="I39">
         <v>711.19</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40" t="s">
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" t="s">
-        <v>105</v>
+        <v>62</v>
+      </c>
+      <c r="F40">
+        <v>52.9</v>
       </c>
       <c r="G40">
-        <v>52.9</v>
+        <v>16</v>
       </c>
       <c r="H40">
-        <v>16</v>
-      </c>
-      <c r="I40">
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" t="s">
-        <v>105</v>
+        <v>62</v>
+      </c>
+      <c r="F41">
+        <v>132.19999999999999</v>
       </c>
       <c r="G41">
-        <v>132.19999999999999</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>32</v>
-      </c>
-      <c r="I41">
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42" t="s">
+        <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F42">
+        <v>859</v>
       </c>
       <c r="G42">
-        <v>859</v>
+        <v>237.5</v>
       </c>
       <c r="H42">
-        <v>237.5</v>
-      </c>
-      <c r="I42">
         <v>275</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" t="s">
-        <v>112</v>
+        <v>66</v>
+      </c>
+      <c r="F43">
+        <v>450</v>
       </c>
       <c r="G43">
-        <v>450</v>
+        <v>308.57</v>
       </c>
       <c r="H43">
-        <v>308.57</v>
-      </c>
-      <c r="I43">
         <v>342.86</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44" t="s">
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F44">
+        <v>4999</v>
       </c>
       <c r="G44">
-        <v>4999</v>
+        <v>2500</v>
       </c>
       <c r="H44">
-        <v>2500</v>
-      </c>
-      <c r="I44">
         <v>3000</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F45">
+        <v>2990</v>
       </c>
       <c r="G45">
-        <v>2990</v>
+        <v>500</v>
       </c>
       <c r="H45">
-        <v>500</v>
-      </c>
-      <c r="I45">
         <v>525</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F46">
+        <v>3999</v>
       </c>
       <c r="G46">
-        <v>3999</v>
+        <v>900</v>
       </c>
       <c r="H46">
-        <v>900</v>
-      </c>
-      <c r="I46">
         <v>990</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F47">
+        <v>23999</v>
       </c>
       <c r="G47">
-        <v>23999</v>
+        <v>2500</v>
       </c>
       <c r="H47">
-        <v>2500</v>
-      </c>
-      <c r="I47">
         <v>3000</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F48">
+        <v>7761.6</v>
       </c>
       <c r="G48">
-        <v>7761.6</v>
+        <v>900</v>
       </c>
       <c r="H48">
-        <v>900</v>
-      </c>
-      <c r="I48">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>91</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" t="s">
-        <v>125</v>
+        <v>73</v>
+      </c>
+      <c r="F49">
+        <v>1751</v>
       </c>
       <c r="G49">
-        <v>1751</v>
+        <v>1200.69</v>
       </c>
       <c r="H49">
-        <v>1200.69</v>
-      </c>
-      <c r="I49">
         <v>1334.1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C50" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" t="s">
-        <v>102</v>
+        <v>60</v>
+      </c>
+      <c r="F50">
+        <v>210</v>
       </c>
       <c r="G50">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="H50">
-        <v>144</v>
-      </c>
-      <c r="I50">
         <v>160</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
-      </c>
-      <c r="C51" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" t="s">
-        <v>130</v>
+        <v>76</v>
+      </c>
+      <c r="F51">
+        <v>310</v>
       </c>
       <c r="G51">
-        <v>310</v>
+        <v>212.57</v>
       </c>
       <c r="H51">
-        <v>212.57</v>
-      </c>
-      <c r="I51">
         <v>236.19</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
-      </c>
-      <c r="C52" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F52">
+        <v>5900</v>
       </c>
       <c r="G52">
-        <v>5900</v>
+        <v>1000</v>
       </c>
       <c r="H52">
-        <v>1000</v>
-      </c>
-      <c r="I52">
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
-      </c>
-      <c r="C53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>91</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" t="s">
-        <v>125</v>
+        <v>73</v>
+      </c>
+      <c r="F53">
+        <v>1349</v>
       </c>
       <c r="G53">
-        <v>1349</v>
+        <v>925.03</v>
       </c>
       <c r="H53">
-        <v>925.03</v>
-      </c>
-      <c r="I53">
         <v>1027.81</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>135</v>
-      </c>
-      <c r="C54" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="F54">
+        <v>429</v>
       </c>
       <c r="G54">
-        <v>429</v>
+        <v>261.76</v>
       </c>
       <c r="H54">
-        <v>261.76</v>
-      </c>
-      <c r="I54">
         <v>290.85000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C55" t="s">
-        <v>138</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
+        <v>91</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F55">
+        <v>8999</v>
       </c>
       <c r="G55">
-        <v>8999</v>
+        <v>950</v>
       </c>
       <c r="H55">
         <v>950</v>
       </c>
-      <c r="I55">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>91</v>
       </c>
       <c r="E56" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F56">
+        <v>8999</v>
       </c>
       <c r="G56">
-        <v>8999</v>
+        <v>250</v>
       </c>
       <c r="H56">
         <v>250</v>
       </c>
-      <c r="I56">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
-      </c>
-      <c r="C57" t="s">
-        <v>142</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57" t="s">
+        <v>91</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="F57">
+        <v>12999</v>
       </c>
       <c r="G57">
-        <v>12999</v>
+        <v>1200</v>
       </c>
       <c r="H57">
-        <v>1200</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>143</v>
-      </c>
-      <c r="C58" t="s">
-        <v>144</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>91</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" t="s">
-        <v>145</v>
+        <v>84</v>
+      </c>
+      <c r="F58">
+        <v>3250</v>
       </c>
       <c r="G58">
-        <v>3250</v>
+        <v>2228.5700000000002</v>
       </c>
       <c r="H58">
-        <v>2228.5700000000002</v>
-      </c>
-      <c r="I58">
         <v>2476.19</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>146</v>
-      </c>
-      <c r="C59" t="s">
-        <v>147</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59" t="s">
+        <v>91</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" t="s">
-        <v>148</v>
+        <v>86</v>
+      </c>
+      <c r="F59">
+        <v>599</v>
       </c>
       <c r="G59">
-        <v>599</v>
+        <v>250</v>
       </c>
       <c r="H59">
-        <v>250</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A60:K72 A2:C2 E2:K2 A3:C59 E3:K59" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B1 A60:B72 A2:B2 E2:H2 A3:B59 E3:H59 C1:H1 C60:H72" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>